--- a/dados_entrada/rentabilidades/rentabilidade_08_2025_agrupada.xlsx
+++ b/dados_entrada/rentabilidades/rentabilidade_08_2025_agrupada.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="62">
   <si>
     <t>linha</t>
   </si>
@@ -55,6 +55,12 @@
     <t>Analisador Portátil</t>
   </si>
   <si>
+    <t>Detector Portátil</t>
+  </si>
+  <si>
+    <t>Detector Fixo</t>
+  </si>
+  <si>
     <t>Diversos Diversos</t>
   </si>
   <si>
@@ -67,18 +73,33 @@
     <t>Analisador Microbiologico</t>
   </si>
   <si>
+    <t>Equipamento Amostragem</t>
+  </si>
+  <si>
+    <t>Sonda Multiparâmetros</t>
+  </si>
+  <si>
     <t>Sonda Diversos</t>
   </si>
   <si>
     <t>Calibração Diversos</t>
   </si>
   <si>
+    <t>Fotometro Portátil</t>
+  </si>
+  <si>
+    <t>Medidor de Vazão Fixo</t>
+  </si>
+  <si>
     <t>Bomba Diversos</t>
   </si>
   <si>
     <t>Bomba Fixa</t>
   </si>
   <si>
+    <t>Sistema Remediação</t>
+  </si>
+  <si>
     <t>Detector Diversos</t>
   </si>
   <si>
@@ -106,28 +127,67 @@
     <t>MicroClip</t>
   </si>
   <si>
+    <t>Panther</t>
+  </si>
+  <si>
+    <t>Innova</t>
+  </si>
+  <si>
+    <t>E3 Point</t>
+  </si>
+  <si>
     <t>Calibração</t>
   </si>
   <si>
     <t>Hora Técnica</t>
   </si>
   <si>
+    <t>Instalação</t>
+  </si>
+  <si>
     <t>Amostrador</t>
   </si>
   <si>
     <t>GeneCount</t>
   </si>
   <si>
+    <t>ISCO</t>
+  </si>
+  <si>
+    <t>YSI</t>
+  </si>
+  <si>
+    <t>EXO</t>
+  </si>
+  <si>
     <t>Solução</t>
   </si>
   <si>
+    <t>9500</t>
+  </si>
+  <si>
+    <t>IQ Standard</t>
+  </si>
+  <si>
+    <t>IQ PLUS</t>
+  </si>
+  <si>
     <t>Bomba</t>
   </si>
   <si>
     <t>Sistema</t>
   </si>
   <si>
+    <t>QED</t>
+  </si>
+  <si>
+    <t>Thermo</t>
+  </si>
+  <si>
     <t>Certificado</t>
+  </si>
+  <si>
+    <t>Treinamento</t>
   </si>
   <si>
     <t>Produto</t>
@@ -497,7 +557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -525,13 +585,13 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="E2">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -542,13 +602,13 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -559,13 +619,13 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -576,13 +636,13 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5">
         <v>27</v>
-      </c>
-      <c r="D5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E5">
-        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -593,13 +653,13 @@
         <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -610,13 +670,13 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="E7">
-        <v>22</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -627,13 +687,13 @@
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="E8">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -641,16 +701,16 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="E9">
-        <v>30</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -658,16 +718,16 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10">
         <v>41</v>
-      </c>
-      <c r="E10">
-        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -678,200 +738,472 @@
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11">
         <v>38</v>
-      </c>
-      <c r="E11">
-        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B12" t="s">
         <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="E12">
-        <v>17</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B13" t="s">
         <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="E13">
-        <v>19</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="E14">
-        <v>16</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="D15" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="E15">
-        <v>14</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D16" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="E16">
-        <v>13</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C17" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" t="s">
+        <v>58</v>
+      </c>
+      <c r="E17">
         <v>35</v>
-      </c>
-      <c r="D17" t="s">
-        <v>38</v>
-      </c>
-      <c r="E17">
-        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D18" t="s">
+        <v>58</v>
+      </c>
+      <c r="E18">
         <v>38</v>
-      </c>
-      <c r="E18">
-        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B19" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D19" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="E19">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C20" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D20" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="E20">
-        <v>29</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="D21" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="E21">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" t="s">
+        <v>47</v>
+      </c>
+      <c r="D22" t="s">
+        <v>58</v>
+      </c>
+      <c r="E22">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" t="s">
+        <v>46</v>
+      </c>
+      <c r="D23" t="s">
+        <v>58</v>
+      </c>
+      <c r="E23">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24" t="s">
+        <v>58</v>
+      </c>
+      <c r="E24">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>6</v>
+      </c>
+      <c r="B25" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" t="s">
+        <v>48</v>
+      </c>
+      <c r="D25" t="s">
+        <v>60</v>
+      </c>
+      <c r="E25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" t="s">
+        <v>6</v>
+      </c>
+      <c r="B26" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26" t="s">
+        <v>49</v>
+      </c>
+      <c r="D26" t="s">
+        <v>58</v>
+      </c>
+      <c r="E26">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" t="s">
+        <v>6</v>
+      </c>
+      <c r="B27" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" t="s">
+        <v>50</v>
+      </c>
+      <c r="D27" t="s">
+        <v>58</v>
+      </c>
+      <c r="E27">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" t="s">
+        <v>6</v>
+      </c>
+      <c r="B28" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" t="s">
+        <v>51</v>
+      </c>
+      <c r="D28" t="s">
+        <v>58</v>
+      </c>
+      <c r="E28">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" t="s">
+        <v>52</v>
+      </c>
+      <c r="D29" t="s">
+        <v>58</v>
+      </c>
+      <c r="E29">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" t="s">
+        <v>26</v>
+      </c>
+      <c r="C30" t="s">
+        <v>53</v>
+      </c>
+      <c r="D30" t="s">
+        <v>58</v>
+      </c>
+      <c r="E30">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" t="s">
+        <v>54</v>
+      </c>
+      <c r="D31" t="s">
+        <v>58</v>
+      </c>
+      <c r="E31">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32" t="s">
+        <v>55</v>
+      </c>
+      <c r="D32" t="s">
+        <v>58</v>
+      </c>
+      <c r="E32">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
+        <v>8</v>
+      </c>
+      <c r="B33" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" t="s">
+        <v>56</v>
+      </c>
+      <c r="D33" t="s">
+        <v>61</v>
+      </c>
+      <c r="E33">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
+        <v>8</v>
+      </c>
+      <c r="B34" t="s">
+        <v>15</v>
+      </c>
+      <c r="C34" t="s">
+        <v>40</v>
+      </c>
+      <c r="D34" t="s">
+        <v>61</v>
+      </c>
+      <c r="E34">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
+        <v>8</v>
+      </c>
+      <c r="B35" t="s">
+        <v>15</v>
+      </c>
+      <c r="C35" t="s">
+        <v>42</v>
+      </c>
+      <c r="D35" t="s">
+        <v>61</v>
+      </c>
+      <c r="E35">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
+        <v>8</v>
+      </c>
+      <c r="B36" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36" t="s">
+        <v>57</v>
+      </c>
+      <c r="D36" t="s">
+        <v>61</v>
+      </c>
+      <c r="E36">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" t="s">
+        <v>61</v>
+      </c>
+      <c r="E37">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" t="s">
         <v>10</v>
       </c>
-      <c r="B22" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" t="s">
-        <v>36</v>
-      </c>
-      <c r="D22" t="s">
-        <v>38</v>
-      </c>
-      <c r="E22">
-        <v>21</v>
+      <c r="B38" t="s">
+        <v>30</v>
+      </c>
+      <c r="C38" t="s">
+        <v>53</v>
+      </c>
+      <c r="D38" t="s">
+        <v>58</v>
+      </c>
+      <c r="E38">
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/dados_entrada/rentabilidades/rentabilidade_08_2025_agrupada.xlsx
+++ b/dados_entrada/rentabilidades/rentabilidade_08_2025_agrupada.xlsx
@@ -1,20 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m.rafael\Desktop\PROJETO_COMISSOES_V2\dados_entrada\rentabilidades\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3908D2F-3ED8-494E-8335-43C19365D997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rentabilidade" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Rentabilidade!$A$1:$E$40</definedName>
+  </definedNames>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="63">
   <si>
     <t>linha</t>
   </si>
@@ -200,13 +209,16 @@
   </si>
   <si>
     <t>Serviço</t>
+  </si>
+  <si>
+    <t>Sonda Serie EXO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -269,13 +281,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -313,7 +333,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -347,6 +367,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -381,9 +402,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -556,11 +578,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E38"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E40"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -577,7 +606,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -594,7 +623,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -611,7 +640,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -628,7 +657,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -645,7 +674,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -662,7 +691,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -679,7 +708,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -696,7 +725,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -713,7 +742,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -730,7 +759,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -747,7 +776,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -764,7 +793,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -781,7 +810,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -798,7 +827,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>5</v>
       </c>
@@ -815,7 +844,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -832,7 +861,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -849,7 +878,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>6</v>
       </c>
@@ -866,7 +895,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>6</v>
       </c>
@@ -883,7 +912,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -900,7 +929,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -917,7 +946,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -934,7 +963,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -951,7 +980,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -968,7 +997,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>6</v>
       </c>
@@ -985,7 +1014,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>6</v>
       </c>
@@ -1002,7 +1031,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -1016,10 +1045,10 @@
         <v>58</v>
       </c>
       <c r="E27">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>6</v>
       </c>
@@ -1036,58 +1065,58 @@
         <v>41</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B29" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="C29" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D29" t="s">
         <v>58</v>
       </c>
       <c r="E29">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>7</v>
       </c>
       <c r="B30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C30" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D30" t="s">
         <v>58</v>
       </c>
       <c r="E30">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>7</v>
       </c>
       <c r="B31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C31" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D31" t="s">
         <v>58</v>
       </c>
       <c r="E31">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>7</v>
       </c>
@@ -1095,50 +1124,50 @@
         <v>27</v>
       </c>
       <c r="C32" t="s">
+        <v>54</v>
+      </c>
+      <c r="D32" t="s">
+        <v>58</v>
+      </c>
+      <c r="E32">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" t="s">
+        <v>27</v>
+      </c>
+      <c r="C33" t="s">
         <v>55</v>
       </c>
-      <c r="D32" t="s">
-        <v>58</v>
-      </c>
-      <c r="E32">
+      <c r="D33" t="s">
+        <v>58</v>
+      </c>
+      <c r="E33">
         <v>44</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
-      <c r="A33" t="s">
-        <v>8</v>
-      </c>
-      <c r="B33" t="s">
-        <v>28</v>
-      </c>
-      <c r="C33" t="s">
-        <v>56</v>
-      </c>
-      <c r="D33" t="s">
-        <v>61</v>
-      </c>
-      <c r="E33">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>8</v>
       </c>
       <c r="B34" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C34" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="D34" t="s">
         <v>61</v>
       </c>
       <c r="E34">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>8</v>
       </c>
@@ -1146,16 +1175,16 @@
         <v>15</v>
       </c>
       <c r="C35" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D35" t="s">
         <v>61</v>
       </c>
       <c r="E35">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>8</v>
       </c>
@@ -1163,50 +1192,85 @@
         <v>15</v>
       </c>
       <c r="C36" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="D36" t="s">
         <v>61</v>
       </c>
       <c r="E36">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B37" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C37" t="s">
-        <v>9</v>
+        <v>57</v>
       </c>
       <c r="D37" t="s">
         <v>61</v>
       </c>
       <c r="E37">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>9</v>
+      </c>
+      <c r="B38" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" t="s">
+        <v>61</v>
+      </c>
+      <c r="E38">
         <v>45</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
-      <c r="A38" t="s">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>10</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B39" t="s">
         <v>30</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C39" t="s">
         <v>53</v>
       </c>
-      <c r="D38" t="s">
-        <v>58</v>
-      </c>
-      <c r="E38">
+      <c r="D39" t="s">
+        <v>58</v>
+      </c>
+      <c r="E39">
         <v>41</v>
       </c>
     </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>8</v>
+      </c>
+      <c r="B40" t="s">
+        <v>15</v>
+      </c>
+      <c r="C40" t="s">
+        <v>33</v>
+      </c>
+      <c r="D40" t="s">
+        <v>60</v>
+      </c>
+      <c r="E40">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:E40" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>